--- a/vault-dalarna-university/02 IHV/Analys/Programkurser olänkade.xlsx
+++ b/vault-dalarna-university/02 IHV/Analys/Programkurser olänkade.xlsx
@@ -7,10 +7,10 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Programkurser olankade" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Programkurser olänkade" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Programkurser olankade'!$A$1:$E$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Programkurser olänkade'!$A$1:$E$21</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>

--- a/vault-dalarna-university/02 IHV/Analys/Programkurser olänkade.xlsx
+++ b/vault-dalarna-university/02 IHV/Analys/Programkurser olänkade.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Programkurser olänkade" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Programkurser olänkade'!$A$1:$E$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Programkurser olänkade'!$A$1:$E$20</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:E20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -634,7 +634,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>VSADA</t>
+          <t>VSSKG</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -644,17 +644,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Programtext avviker från kursplanens namn</t>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Programtext `Examensarbete i omvårdnad – demensvård` ≠ kursplanens namn `Examensarbete i omvårdnad - demensvård` (kurskod `AVÅ28V`); rad: - [[AVÅ28V|Examensarbete i omvårdnad – demensvård]], 15 hp</t>
+          <t>`Introduktion omvårdnad och etik - Huvudområde Omvårdnad` (15 hp); rad: - Introduktion omvårdnad och etik - Huvudområde Omvårdnad, 15 hp</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=VSADA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=VSSKG</t>
         </is>
       </c>
     </row>
@@ -676,7 +676,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>`Introduktion omvårdnad och etik - Huvudområde Omvårdnad` (15 hp); rad: - Introduktion omvårdnad och etik - Huvudområde Omvårdnad, 15 hp</t>
+          <t>`Metoder för evidensbaserad vård I - Huvudområde Omvårdnad` (7,5 hp); rad: - Metoder för evidensbaserad vård I - Huvudområde Omvårdnad, 7,5 hp</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>`Metoder för evidensbaserad vård I - Huvudområde Omvårdnad` (7,5 hp); rad: - Metoder för evidensbaserad vård I - Huvudområde Omvårdnad, 7,5 hp</t>
+          <t>`Människans grundläggande omvårdnadsbehov - Huvudområde Omvårdnad` (10,5 hp); rad: - Människans grundläggande omvårdnadsbehov - Huvudområde Omvårdnad, 10,5 hp</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -730,7 +730,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>`Människans grundläggande omvårdnadsbehov - Huvudområde Omvårdnad` (10,5 hp); rad: - Människans grundläggande omvårdnadsbehov - Huvudområde Omvårdnad, 10,5 hp</t>
+          <t>`Människa, hälsa och samhälle - Huvudområde Omvårdnad` (7,5 hp); rad: - Människa, hälsa och samhälle - Huvudområde Omvårdnad, 7,5 hp</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -757,7 +757,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>`Människa, hälsa och samhälle - Huvudområde Omvårdnad` (7,5 hp); rad: - Människa, hälsa och samhälle - Huvudområde Omvårdnad, 7,5 hp</t>
+          <t>`Metoder och teorier vid symtom och tecken på hälsa/ohälsa I - Huvudområde Omvårdnad` (30 hp); rad: - Metoder och teorier vid symtom och tecken på hälsa/ohälsa I - Huvudområde Omvårdnad, 30 hp</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>`Metoder och teorier vid symtom och tecken på hälsa/ohälsa I - Huvudområde Omvårdnad` (30 hp); rad: - Metoder och teorier vid symtom och tecken på hälsa/ohälsa I - Huvudområde Omvårdnad, 30 hp</t>
+          <t>`Personcentrerad vård inom somatisk vård - Huvudområde Omvårdnad` (15 hp); rad: - Personcentrerad vård inom somatisk vård - Huvudområde Omvårdnad, 15 hp</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -811,7 +811,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>`Personcentrerad vård inom somatisk vård - Huvudområde Omvårdnad` (15 hp); rad: - Personcentrerad vård inom somatisk vård - Huvudområde Omvårdnad, 15 hp</t>
+          <t>`Metoder och teorier vid symtom och tecken på hälsa/ohälsa II - Huvudområde Omvårdnad` (7,5 hp); rad: - Metoder och teorier vid symtom och tecken på hälsa/ohälsa II - Huvudområde Omvårdnad, 7,5 hp</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -838,7 +838,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>`Metoder och teorier vid symtom och tecken på hälsa/ohälsa II - Huvudområde Omvårdnad` (7,5 hp); rad: - Metoder och teorier vid symtom och tecken på hälsa/ohälsa II - Huvudområde Omvårdnad, 7,5 hp</t>
+          <t>`Ledarskap och teamarbete - Huvudområde Omvårdnad` (7,5 hp); rad: - Ledarskap och teamarbete - Huvudområde Omvårdnad, 7,5 hp</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>`Ledarskap och teamarbete - Huvudområde Omvårdnad` (7,5 hp); rad: - Ledarskap och teamarbete - Huvudområde Omvårdnad, 7,5 hp</t>
+          <t>`Personcentrerad vård inom olika vårdsammanhang - Huvudområde Omvårdnad` (22,5 hp); rad: - Personcentrerad vård inom olika vårdsammanhang - Huvudområde Omvårdnad, 22,5 hp</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -892,7 +892,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>`Personcentrerad vård inom olika vårdsammanhang - Huvudområde Omvårdnad` (22,5 hp); rad: - Personcentrerad vård inom olika vårdsammanhang - Huvudområde Omvårdnad, 22,5 hp</t>
+          <t>`Personcentrerad vård inom psykiatrisk vård - Huvudområde Omvårdnad` (7,5 hp); rad: - Personcentrerad vård inom psykiatrisk vård - Huvudområde Omvårdnad, 7,5 hp</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -919,7 +919,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>`Personcentrerad vård inom psykiatrisk vård - Huvudområde Omvårdnad` (7,5 hp); rad: - Personcentrerad vård inom psykiatrisk vård - Huvudområde Omvårdnad, 7,5 hp</t>
+          <t>`Metoder för evidensbaserad vård II - Huvudområde Omvårdnad` (7,5 hp); rad: - Metoder för evidensbaserad vård II - Huvudområde Omvårdnad, 7,5 hp</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -946,7 +946,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>`Metoder för evidensbaserad vård II - Huvudområde Omvårdnad` (7,5 hp); rad: - Metoder för evidensbaserad vård II - Huvudområde Omvårdnad, 7,5 hp</t>
+          <t>`Examensarbete i omvårdnad - Huvudområde Omvårdnad` (15 hp); rad: - Examensarbete i omvårdnad - Huvudområde Omvårdnad, 15 hp</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -973,7 +973,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>`Examensarbete i omvårdnad - Huvudområde Omvårdnad` (15 hp); rad: - Examensarbete i omvårdnad - Huvudområde Omvårdnad, 15 hp</t>
+          <t>`Personcentrerad vård med fördjupning inom omvårdnad - Huvudområde Omvårdnad` (7,5 hp); rad: - Personcentrerad vård med fördjupning inom omvårdnad - Huvudområde Omvårdnad, 7,5 hp</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -982,35 +982,8 @@
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>VSSKG</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Utbildningsplan</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>`Personcentrerad vård med fördjupning inom omvårdnad - Huvudområde Omvårdnad` (7,5 hp); rad: - Personcentrerad vård med fördjupning inom omvårdnad - Huvudområde Omvårdnad, 7,5 hp</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=VSSKG</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:E21"/>
+  <autoFilter ref="A1:E20"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId2"/>
@@ -1050,8 +1023,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E19" r:id="rId36"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A20" r:id="rId37"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A21" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="rId40"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/02 IHV/Analys/Programkurser olänkade.xlsx
+++ b/vault-dalarna-university/02 IHV/Analys/Programkurser olänkade.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Programkurser olänkade" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Programkurser olänkade'!$A$1:$E$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Programkurser olänkade'!$A$1:$E$19</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E20"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -644,12 +644,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Kurs finns aktivt men scrapern länkade inte</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>`Introduktion omvårdnad och etik - Huvudområde Omvårdnad` (15 hp); rad: - Introduktion omvårdnad och etik - Huvudområde Omvårdnad, 15 hp</t>
+          <t>`Metoder för evidensbaserad vård I - Huvudområde Omvårdnad` (7,5 hp); rad: - Metoder för evidensbaserad vård I - Huvudområde Omvårdnad, 7,5 hp</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -671,12 +671,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Kurs finns aktivt men scrapern länkade inte</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>`Metoder för evidensbaserad vård I - Huvudområde Omvårdnad` (7,5 hp); rad: - Metoder för evidensbaserad vård I - Huvudområde Omvårdnad, 7,5 hp</t>
+          <t>`Människans grundläggande omvårdnadsbehov - Huvudområde Omvårdnad` (10,5 hp); rad: - Människans grundläggande omvårdnadsbehov - Huvudområde Omvårdnad, 10,5 hp</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -698,12 +698,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Kurs finns aktivt men scrapern länkade inte</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>`Människans grundläggande omvårdnadsbehov - Huvudområde Omvårdnad` (10,5 hp); rad: - Människans grundläggande omvårdnadsbehov - Huvudområde Omvårdnad, 10,5 hp</t>
+          <t>`Människa, hälsa och samhälle - Huvudområde Omvårdnad` (7,5 hp); rad: - Människa, hälsa och samhälle - Huvudområde Omvårdnad, 7,5 hp</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -725,12 +725,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Kurs finns aktivt men scrapern länkade inte</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>`Människa, hälsa och samhälle - Huvudområde Omvårdnad` (7,5 hp); rad: - Människa, hälsa och samhälle - Huvudområde Omvårdnad, 7,5 hp</t>
+          <t>`Metoder och teorier vid symtom och tecken på hälsa/ohälsa I - Huvudområde Omvårdnad` (30 hp); rad: - Metoder och teorier vid symtom och tecken på hälsa/ohälsa I - Huvudområde Omvårdnad, 30 hp</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Kurs finns aktivt men scrapern länkade inte</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>`Metoder och teorier vid symtom och tecken på hälsa/ohälsa I - Huvudområde Omvårdnad` (30 hp); rad: - Metoder och teorier vid symtom och tecken på hälsa/ohälsa I - Huvudområde Omvårdnad, 30 hp</t>
+          <t>`Personcentrerad vård inom somatisk vård - Huvudområde Omvårdnad` (15 hp); rad: - Personcentrerad vård inom somatisk vård - Huvudområde Omvårdnad, 15 hp</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -779,12 +779,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Kurs finns aktivt men scrapern länkade inte</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>`Personcentrerad vård inom somatisk vård - Huvudområde Omvårdnad` (15 hp); rad: - Personcentrerad vård inom somatisk vård - Huvudområde Omvårdnad, 15 hp</t>
+          <t>`Metoder och teorier vid symtom och tecken på hälsa/ohälsa II - Huvudområde Omvårdnad` (7,5 hp); rad: - Metoder och teorier vid symtom och tecken på hälsa/ohälsa II - Huvudområde Omvårdnad, 7,5 hp</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -806,12 +806,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Kurs finns aktivt men scrapern länkade inte</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>`Metoder och teorier vid symtom och tecken på hälsa/ohälsa II - Huvudområde Omvårdnad` (7,5 hp); rad: - Metoder och teorier vid symtom och tecken på hälsa/ohälsa II - Huvudområde Omvårdnad, 7,5 hp</t>
+          <t>`Ledarskap och teamarbete - Huvudområde Omvårdnad` (7,5 hp); rad: - Ledarskap och teamarbete - Huvudområde Omvårdnad, 7,5 hp</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -833,12 +833,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Kurs finns aktivt men scrapern länkade inte</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>`Ledarskap och teamarbete - Huvudområde Omvårdnad` (7,5 hp); rad: - Ledarskap och teamarbete - Huvudområde Omvårdnad, 7,5 hp</t>
+          <t>`Personcentrerad vård inom olika vårdsammanhang - Huvudområde Omvårdnad` (22,5 hp); rad: - Personcentrerad vård inom olika vårdsammanhang - Huvudområde Omvårdnad, 22,5 hp</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Kurs finns aktivt men scrapern länkade inte</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>`Personcentrerad vård inom olika vårdsammanhang - Huvudområde Omvårdnad` (22,5 hp); rad: - Personcentrerad vård inom olika vårdsammanhang - Huvudområde Omvårdnad, 22,5 hp</t>
+          <t>`Personcentrerad vård inom psykiatrisk vård - Huvudområde Omvårdnad` (7,5 hp); rad: - Personcentrerad vård inom psykiatrisk vård - Huvudområde Omvårdnad, 7,5 hp</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -887,12 +887,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Kurs finns aktivt men scrapern länkade inte</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>`Personcentrerad vård inom psykiatrisk vård - Huvudområde Omvårdnad` (7,5 hp); rad: - Personcentrerad vård inom psykiatrisk vård - Huvudområde Omvårdnad, 7,5 hp</t>
+          <t>`Metoder för evidensbaserad vård II - Huvudområde Omvårdnad` (7,5 hp); rad: - Metoder för evidensbaserad vård II - Huvudområde Omvårdnad, 7,5 hp</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Kurs finns aktivt men scrapern länkade inte</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>`Metoder för evidensbaserad vård II - Huvudområde Omvårdnad` (7,5 hp); rad: - Metoder för evidensbaserad vård II - Huvudområde Omvårdnad, 7,5 hp</t>
+          <t>`Examensarbete i omvårdnad - Huvudområde Omvårdnad` (15 hp); rad: - Examensarbete i omvårdnad - Huvudområde Omvårdnad, 15 hp</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -941,12 +941,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Kurs finns aktivt men scrapern länkade inte</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>`Examensarbete i omvårdnad - Huvudområde Omvårdnad` (15 hp); rad: - Examensarbete i omvårdnad - Huvudområde Omvårdnad, 15 hp</t>
+          <t>`Personcentrerad vård med fördjupning inom omvårdnad - Huvudområde Omvårdnad` (7,5 hp); rad: - Personcentrerad vård med fördjupning inom omvårdnad - Huvudområde Omvårdnad, 7,5 hp</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -955,35 +955,8 @@
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>VSSKG</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Utbildningsplan</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>`Personcentrerad vård med fördjupning inom omvårdnad - Huvudområde Omvårdnad` (7,5 hp); rad: - Personcentrerad vård med fördjupning inom omvårdnad - Huvudområde Omvårdnad, 7,5 hp</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=VSSKG</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:E20"/>
+  <autoFilter ref="A1:E19"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId2"/>
@@ -1021,8 +994,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E18" r:id="rId34"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A19" r:id="rId35"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E19" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A20" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="rId38"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/02 IHV/Analys/Programkurser olänkade.xlsx
+++ b/vault-dalarna-university/02 IHV/Analys/Programkurser olänkade.xlsx
@@ -644,12 +644,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Kurs finns aktivt men scrapern länkade inte</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>`Metoder för evidensbaserad vård I - Huvudområde Omvårdnad` (7,5 hp); rad: - Metoder för evidensbaserad vård I - Huvudområde Omvårdnad, 7,5 hp</t>
+          <t>Programtext `Metoder för evidensbaserad vård I - Huvudområde Omvårdnad` ≠ kursplanens namn `Metoder för evidensbaserad vård I` (kurskod `GVÅ2N9`); rad: - [[GVÅ2N9|Metoder för evidensbaserad vård I - Huvudområde Omvårdnad]], 7,5 hp</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -671,12 +671,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Kurs finns aktivt men scrapern länkade inte</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>`Människans grundläggande omvårdnadsbehov - Huvudområde Omvårdnad` (10,5 hp); rad: - Människans grundläggande omvårdnadsbehov - Huvudområde Omvårdnad, 10,5 hp</t>
+          <t>Programtext `Människans grundläggande omvårdnadsbehov - Huvudområde Omvårdnad` ≠ kursplanens namn `Människans grundläggande omvårdnadsbehov` (kurskod `GVÅ2RA`); rad: - [[GVÅ2RA|Människans grundläggande omvårdnadsbehov - Huvudområde Omvårdnad]], 10,5 hp</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -698,12 +698,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Kurs finns aktivt men scrapern länkade inte</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>`Människa, hälsa och samhälle - Huvudområde Omvårdnad` (7,5 hp); rad: - Människa, hälsa och samhälle - Huvudområde Omvårdnad, 7,5 hp</t>
+          <t>Programtext `Människa, hälsa och samhälle - Huvudområde Omvårdnad` ≠ kursplanens namn `Människa, hälsa och samhälle` (kurskod `GVÅ2AP`); rad: - [[GVÅ2AP|Människa, hälsa och samhälle - Huvudområde Omvårdnad]], 7,5 hp</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -725,12 +725,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Kurs finns aktivt men scrapern länkade inte</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>`Metoder och teorier vid symtom och tecken på hälsa/ohälsa I - Huvudområde Omvårdnad` (30 hp); rad: - Metoder och teorier vid symtom och tecken på hälsa/ohälsa I - Huvudområde Omvårdnad, 30 hp</t>
+          <t>Programtext `Metoder och teorier vid symtom och tecken på hälsa/ohälsa I - Huvudområde Omvårdnad` ≠ kursplanens namn `Metoder och teorier vid symtom och tecken på hälsa/ohälsa I` (kurskod `VÅ1053`); rad: - [[VÅ1053|Metoder och teorier vid symtom och tecken på hälsa/ohälsa I - Huvudområde Omvårdnad]], 30 hp</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Kurs finns aktivt men scrapern länkade inte</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>`Personcentrerad vård inom somatisk vård - Huvudområde Omvårdnad` (15 hp); rad: - Personcentrerad vård inom somatisk vård - Huvudområde Omvårdnad, 15 hp</t>
+          <t>Programtext `Personcentrerad vård inom somatisk vård - Huvudområde Omvårdnad` ≠ kursplanens namn `Personcentrerad vård inom somatisk vård` (kurskod `GVÅ384`); rad: - [[GVÅ384|Personcentrerad vård inom somatisk vård - Huvudområde Omvårdnad]], 15 hp</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -779,12 +779,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Kurs finns aktivt men scrapern länkade inte</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>`Metoder och teorier vid symtom och tecken på hälsa/ohälsa II - Huvudområde Omvårdnad` (7,5 hp); rad: - Metoder och teorier vid symtom och tecken på hälsa/ohälsa II - Huvudområde Omvårdnad, 7,5 hp</t>
+          <t>Programtext `Metoder och teorier vid symtom och tecken på hälsa/ohälsa II - Huvudområde Omvårdnad` ≠ kursplanens namn `Metoder och teorier vid symtom och tecken på hälsa/ohälsa II` (kurskod `GVÅ37Y`); rad: - [[GVÅ37Y|Metoder och teorier vid symtom och tecken på hälsa/ohälsa II - Huvudområde Omvårdnad]], 7,5 hp</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -806,12 +806,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Kurs finns aktivt men scrapern länkade inte</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>`Ledarskap och teamarbete - Huvudområde Omvårdnad` (7,5 hp); rad: - Ledarskap och teamarbete - Huvudområde Omvårdnad, 7,5 hp</t>
+          <t>Programtext `Ledarskap och teamarbete - Huvudområde Omvårdnad` ≠ kursplanens namn `Ledarskap och teamarbete` (kurskod `GVÅ2S3`); rad: - [[GVÅ2S3|Ledarskap och teamarbete - Huvudområde Omvårdnad]], 7,5 hp</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -833,12 +833,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Kurs finns aktivt men scrapern länkade inte</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>`Personcentrerad vård inom olika vårdsammanhang - Huvudområde Omvårdnad` (22,5 hp); rad: - Personcentrerad vård inom olika vårdsammanhang - Huvudområde Omvårdnad, 22,5 hp</t>
+          <t>Programtext `Personcentrerad vård inom olika vårdsammanhang - Huvudområde Omvårdnad` ≠ kursplanens namn `Personcentrerad vård inom olika vårdsammanhang` (kurskod `GVÅ2H6`); rad: - [[GVÅ2H6|Personcentrerad vård inom olika vårdsammanhang - Huvudområde Omvårdnad]], 22,5 hp</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Kurs finns aktivt men scrapern länkade inte</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>`Personcentrerad vård inom psykiatrisk vård - Huvudområde Omvårdnad` (7,5 hp); rad: - Personcentrerad vård inom psykiatrisk vård - Huvudområde Omvårdnad, 7,5 hp</t>
+          <t>Programtext `Personcentrerad vård inom psykiatrisk vård - Huvudområde Omvårdnad` ≠ kursplanens namn `Personcentrerad vård inom psykiatrisk vård` (kurskod `GVÅ2HM`); rad: - [[GVÅ2HM|Personcentrerad vård inom psykiatrisk vård - Huvudområde Omvårdnad]], 7,5 hp</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -887,12 +887,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Kurs finns aktivt men scrapern länkade inte</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>`Metoder för evidensbaserad vård II - Huvudområde Omvårdnad` (7,5 hp); rad: - Metoder för evidensbaserad vård II - Huvudområde Omvårdnad, 7,5 hp</t>
+          <t>Programtext `Metoder för evidensbaserad vård II - Huvudområde Omvårdnad` ≠ kursplanens namn `Metoder för evidensbaserad vård II` (kurskod `GVÅ2ZY`); rad: - [[GVÅ2ZY|Metoder för evidensbaserad vård II - Huvudområde Omvårdnad]], 7,5 hp</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Kurs finns aktivt men scrapern länkade inte</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>`Examensarbete i omvårdnad - Huvudområde Omvårdnad` (15 hp); rad: - Examensarbete i omvårdnad - Huvudområde Omvårdnad, 15 hp</t>
+          <t>Programtext `Examensarbete i omvårdnad - Huvudområde Omvårdnad` ≠ kursplanens namn `Examensarbete i omvårdnad` (kurskod `GVÅ36W`); rad: - [[GVÅ36W|Examensarbete i omvårdnad - Huvudområde Omvårdnad]], 15 hp</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -941,12 +941,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Kurs finns aktivt men scrapern länkade inte</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>`Personcentrerad vård med fördjupning inom omvårdnad - Huvudområde Omvårdnad` (7,5 hp); rad: - Personcentrerad vård med fördjupning inom omvårdnad - Huvudområde Omvårdnad, 7,5 hp</t>
+          <t>Programtext `Personcentrerad vård med fördjupning inom omvårdnad - Huvudområde Omvårdnad` ≠ kursplanens namn `Personcentrerad vård med fördjupning inom omvårdnad` (kurskod `GVÅ2ZG`); rad: - [[GVÅ2ZG|Personcentrerad vård med fördjupning inom omvårdnad - Huvudområde Omvårdnad]], 7,5 hp</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">

--- a/vault-dalarna-university/02 IHV/Analys/Programkurser olänkade.xlsx
+++ b/vault-dalarna-university/02 IHV/Analys/Programkurser olänkade.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Programkurser olänkade" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Programkurser olänkade'!$A$1:$E$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Programkurser olänkade'!$A$1:$E$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -631,332 +631,8 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>VSSKG</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Utbildningsplan</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Programtext avviker från kursplanens namn</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Programtext `Metoder för evidensbaserad vård I - Huvudområde Omvårdnad` ≠ kursplanens namn `Metoder för evidensbaserad vård I` (kurskod `GVÅ2N9`); rad: - [[GVÅ2N9|Metoder för evidensbaserad vård I - Huvudområde Omvårdnad]], 7,5 hp</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=VSSKG</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>VSSKG</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Utbildningsplan</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Programtext avviker från kursplanens namn</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Programtext `Människans grundläggande omvårdnadsbehov - Huvudområde Omvårdnad` ≠ kursplanens namn `Människans grundläggande omvårdnadsbehov` (kurskod `GVÅ2RA`); rad: - [[GVÅ2RA|Människans grundläggande omvårdnadsbehov - Huvudområde Omvårdnad]], 10,5 hp</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=VSSKG</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>VSSKG</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Utbildningsplan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Programtext avviker från kursplanens namn</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Programtext `Människa, hälsa och samhälle - Huvudområde Omvårdnad` ≠ kursplanens namn `Människa, hälsa och samhälle` (kurskod `GVÅ2AP`); rad: - [[GVÅ2AP|Människa, hälsa och samhälle - Huvudområde Omvårdnad]], 7,5 hp</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=VSSKG</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>VSSKG</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Utbildningsplan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Programtext avviker från kursplanens namn</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Programtext `Metoder och teorier vid symtom och tecken på hälsa/ohälsa I - Huvudområde Omvårdnad` ≠ kursplanens namn `Metoder och teorier vid symtom och tecken på hälsa/ohälsa I` (kurskod `VÅ1053`); rad: - [[VÅ1053|Metoder och teorier vid symtom och tecken på hälsa/ohälsa I - Huvudområde Omvårdnad]], 30 hp</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=VSSKG</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>VSSKG</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Utbildningsplan</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Programtext avviker från kursplanens namn</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Programtext `Personcentrerad vård inom somatisk vård - Huvudområde Omvårdnad` ≠ kursplanens namn `Personcentrerad vård inom somatisk vård` (kurskod `GVÅ384`); rad: - [[GVÅ384|Personcentrerad vård inom somatisk vård - Huvudområde Omvårdnad]], 15 hp</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=VSSKG</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>VSSKG</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Utbildningsplan</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Programtext avviker från kursplanens namn</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Programtext `Metoder och teorier vid symtom och tecken på hälsa/ohälsa II - Huvudområde Omvårdnad` ≠ kursplanens namn `Metoder och teorier vid symtom och tecken på hälsa/ohälsa II` (kurskod `GVÅ37Y`); rad: - [[GVÅ37Y|Metoder och teorier vid symtom och tecken på hälsa/ohälsa II - Huvudområde Omvårdnad]], 7,5 hp</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=VSSKG</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>VSSKG</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Utbildningsplan</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Programtext avviker från kursplanens namn</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Programtext `Ledarskap och teamarbete - Huvudområde Omvårdnad` ≠ kursplanens namn `Ledarskap och teamarbete` (kurskod `GVÅ2S3`); rad: - [[GVÅ2S3|Ledarskap och teamarbete - Huvudområde Omvårdnad]], 7,5 hp</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=VSSKG</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>VSSKG</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Utbildningsplan</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Programtext avviker från kursplanens namn</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Programtext `Personcentrerad vård inom olika vårdsammanhang - Huvudområde Omvårdnad` ≠ kursplanens namn `Personcentrerad vård inom olika vårdsammanhang` (kurskod `GVÅ2H6`); rad: - [[GVÅ2H6|Personcentrerad vård inom olika vårdsammanhang - Huvudområde Omvårdnad]], 22,5 hp</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=VSSKG</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>VSSKG</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Utbildningsplan</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Programtext avviker från kursplanens namn</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Programtext `Personcentrerad vård inom psykiatrisk vård - Huvudområde Omvårdnad` ≠ kursplanens namn `Personcentrerad vård inom psykiatrisk vård` (kurskod `GVÅ2HM`); rad: - [[GVÅ2HM|Personcentrerad vård inom psykiatrisk vård - Huvudområde Omvårdnad]], 7,5 hp</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=VSSKG</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>VSSKG</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Utbildningsplan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Programtext avviker från kursplanens namn</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Programtext `Metoder för evidensbaserad vård II - Huvudområde Omvårdnad` ≠ kursplanens namn `Metoder för evidensbaserad vård II` (kurskod `GVÅ2ZY`); rad: - [[GVÅ2ZY|Metoder för evidensbaserad vård II - Huvudområde Omvårdnad]], 7,5 hp</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=VSSKG</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>VSSKG</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Utbildningsplan</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Programtext avviker från kursplanens namn</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Programtext `Examensarbete i omvårdnad - Huvudområde Omvårdnad` ≠ kursplanens namn `Examensarbete i omvårdnad` (kurskod `GVÅ36W`); rad: - [[GVÅ36W|Examensarbete i omvårdnad - Huvudområde Omvårdnad]], 15 hp</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=VSSKG</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>VSSKG</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Utbildningsplan</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Programtext avviker från kursplanens namn</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Programtext `Personcentrerad vård med fördjupning inom omvårdnad - Huvudområde Omvårdnad` ≠ kursplanens namn `Personcentrerad vård med fördjupning inom omvårdnad` (kurskod `GVÅ2ZG`); rad: - [[GVÅ2ZG|Personcentrerad vård med fördjupning inom omvårdnad - Huvudområde Omvårdnad]], 7,5 hp</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=VSSKG</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:E19"/>
+  <autoFilter ref="A1:E7"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId2"/>
@@ -970,30 +646,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A7" r:id="rId11"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A8" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A9" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A10" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A11" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A12" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A13" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E13" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A14" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E14" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A15" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A16" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E16" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A17" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E17" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A18" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E18" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A19" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E19" r:id="rId36"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/02 IHV/Analys/Programkurser olänkade.xlsx
+++ b/vault-dalarna-university/02 IHV/Analys/Programkurser olänkade.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Programkurser olänkade" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Programkurser olänkade'!$A$1:$E$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Programkurser olänkade'!$A$1:$E$6</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -526,7 +526,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>VBSKA</t>
+          <t>VGSEA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -536,24 +536,24 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Kursraden ser avbruten/feltrycklig ut</t>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>`) kurser som krävs för magisterexamen` (60 hp); rad: - ) kurser som krävs för magisterexamen, 60 hp</t>
+          <t>`Strategier för implementering av förbättringsarbete i hälso-sjukvård` (7,5 hp); rad: - Strategier för implementering av förbättringsarbete i hälso-sjukvård, 7,5 hp</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=VBSKA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=VGSEA</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>VGSEA</t>
+          <t>VIDRG</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -568,19 +568,19 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>`Strategier för implementering av förbättringsarbete i hälso-sjukvård` (7,5 hp); rad: - Strategier för implementering av förbättringsarbete i hälso-sjukvård, 7,5 hp</t>
+          <t>`Media och kommunikation inom idrott` (7,5hp); rad: - Media och kommunikation inom idrott, 7,5hp</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=VGSEA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=VIDRG</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>VIDRG</t>
+          <t>VSADA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -595,44 +595,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>`Media och kommunikation inom idrott` (7,5hp); rad: - Media och kommunikation inom idrott, 7,5hp</t>
+          <t>`Personcentrerad vård av personer med demens` (7,5 hp); rad: - Personcentrerad vård av personer med demens, 7,5 hp</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=VIDRG</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>VSADA</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Utbildningsplan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>`Personcentrerad vård av personer med demens` (7,5 hp); rad: - Personcentrerad vård av personer med demens, 7,5 hp</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=VSADA</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E7"/>
+  <autoFilter ref="A1:E6"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId2"/>
@@ -644,8 +617,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A6" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A7" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId12"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/02 IHV/Analys/Programkurser olänkade.xlsx
+++ b/vault-dalarna-university/02 IHV/Analys/Programkurser olänkade.xlsx
@@ -487,7 +487,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>`Gravididet, förlossning och postpartumvård 1` (7,5 hp); rad: - Gravididet, förlossning och postpartumvård 1, 7,5 hp</t>
+          <t>`Gravididet, förlossning och postpartumvård 1` (7,5 hp)</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -514,7 +514,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>`Gravididet, förlossning och postpartumvård 2` (6 hp); rad: - Gravididet, förlossning och postpartumvård 2, 6 hp</t>
+          <t>`Gravididet, förlossning och postpartumvård 2` (6 hp)</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -541,7 +541,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>`Strategier för implementering av förbättringsarbete i hälso-sjukvård` (7,5 hp); rad: - Strategier för implementering av förbättringsarbete i hälso-sjukvård, 7,5 hp</t>
+          <t>`Strategier för implementering av förbättringsarbete i hälso-sjukvård` (7,5 hp)</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -568,7 +568,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>`Media och kommunikation inom idrott` (7,5hp); rad: - Media och kommunikation inom idrott, 7,5hp</t>
+          <t>`Media och kommunikation inom idrott` (7,5hp)</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -595,7 +595,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>`Personcentrerad vård av personer med demens` (7,5 hp); rad: - Personcentrerad vård av personer med demens, 7,5 hp</t>
+          <t>`Personcentrerad vård av personer med demens` (7,5 hp)</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">

--- a/vault-dalarna-university/02 IHV/Analys/Programkurser olänkade.xlsx
+++ b/vault-dalarna-university/02 IHV/Analys/Programkurser olänkade.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Programkurser olänkade" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Programkurser olänkade'!$A$1:$E$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Programkurser olänkade'!$A$1:$G$6</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,14 +432,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="70" customWidth="1" min="4" max="4"/>
-    <col width="70" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
+    <col width="70" customWidth="1" min="6" max="6"/>
+    <col width="70" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -455,15 +457,25 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>Fastställd</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Reviderad</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>Problem</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Detalj</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Länk</t>
         </is>
@@ -482,15 +494,21 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>2019-09-10</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>Kursnamnet finns varken aktivt eller nedlagt</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>`Gravididet, förlossning och postpartumvård 1` (7,5 hp)</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=VBSKA</t>
         </is>
@@ -509,15 +527,21 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
+          <t>2019-09-10</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>Kursnamnet finns varken aktivt eller nedlagt</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>`Gravididet, förlossning och postpartumvård 2` (6 hp)</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=VBSKA</t>
         </is>
@@ -536,15 +560,21 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
+          <t>2021-03-04</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>Kursnamnet finns varken aktivt eller nedlagt</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>`Strategier för implementering av förbättringsarbete i hälso-sjukvård` (7,5 hp)</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=VGSEA</t>
         </is>
@@ -563,15 +593,21 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
+          <t>2025-01-15</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>Kursnamnet finns varken aktivt eller nedlagt</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>`Media och kommunikation inom idrott` (7,5hp)</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=VIDRG</t>
         </is>
@@ -590,33 +626,39 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
+          <t>2023-01-09</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>Kursnamnet finns varken aktivt eller nedlagt</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>`Personcentrerad vård av personer med demens` (7,5 hp)</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=VSADA</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E6"/>
+  <autoFilter ref="A1:G6"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G2" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A3" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G3" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A4" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E4" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G4" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A5" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G5" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A6" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G6" r:id="rId10"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/02 IHV/Analys/Programkurser olänkade.xlsx
+++ b/vault-dalarna-university/02 IHV/Analys/Programkurser olänkade.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Programkurser olänkade" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Programkurser olänkade'!$A$1:$G$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Programkurser olänkade'!$A$1:$H$6</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -441,7 +441,8 @@
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="28" customWidth="1" min="5" max="5"/>
     <col width="70" customWidth="1" min="6" max="6"/>
-    <col width="70" customWidth="1" min="7" max="7"/>
+    <col width="28" customWidth="1" min="7" max="7"/>
+    <col width="70" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -477,6 +478,11 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>Förslag</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>Länk</t>
         </is>
       </c>
@@ -500,7 +506,7 @@
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -508,7 +514,12 @@
           <t>`Gravididet, förlossning och postpartumvård 1` (7,5 hp)</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>`Graviditet, förlossning och postpartumvård I` (kurskod `ASR29T`)</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=VBSKA</t>
         </is>
@@ -533,7 +544,7 @@
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -541,7 +552,12 @@
           <t>`Gravididet, förlossning och postpartumvård 2` (6 hp)</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>`Graviditet, förlossning och postpartumvård II` (kurskod `ASR2AD`)</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=VBSKA</t>
         </is>
@@ -566,7 +582,7 @@
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -574,7 +590,12 @@
           <t>`Strategier för implementering av förbättringsarbete i hälso-sjukvård` (7,5 hp)</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>`Strategier för implementering av förbättringsarbete i hälso- och sjukvård` (kurskod `ASR2CG`)</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=VGSEA</t>
         </is>
@@ -599,7 +620,7 @@
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -607,7 +628,12 @@
           <t>`Media och kommunikation inom idrott` (7,5hp)</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>`Medier och kommunikation inom idrott` (kurskod `GIH3GF`)</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=VIDRG</t>
         </is>
@@ -632,7 +658,7 @@
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -640,25 +666,30 @@
           <t>`Personcentrerad vård av personer med demens` (7,5 hp)</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>`Personcentrerad vård för personer med demens` (kurskod `VÅ3127`)</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=VSADA</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G6"/>
+  <autoFilter ref="A1:H6"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G2" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H2" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A3" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G3" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H3" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A4" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G4" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H4" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A5" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G5" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H5" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A6" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G6" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H6" r:id="rId10"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
